--- a/registration_forms/021_care_coordination_technology_showcase_registration_form--registration_forms.xlsx
+++ b/registration_forms/021_care_coordination_technology_showcase_registration_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -854,8 +854,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'it/health_tech_specialist',_'value':_'tech_specialist'}</t>
+          <t>it/health_tech_specialist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'IT/Health Tech Specialist', 'value': 'tech_specialist'}</t>
+          <t>IT/Health Tech Specialist</t>
         </is>
       </c>
     </row>
@@ -900,12 +900,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'care_coordinator/manager',_'value':_'care_coordinator'}</t>
+          <t>care_coordinator/manager</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Care Coordinator/Manager', 'value': 'care_coordinator'}</t>
+          <t>Care Coordinator/Manager</t>
         </is>
       </c>
     </row>
@@ -917,12 +917,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'clinical_administrator',_'value':_'clinical_admin'}</t>
+          <t>clinical_administrator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Clinical Administrator', 'value': 'clinical_admin'}</t>
+          <t>Clinical Administrator</t>
         </is>
       </c>
     </row>
@@ -934,12 +934,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'nurse_manager',_'value':_'nurse_manager'}</t>
+          <t>nurse_manager</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Nurse Manager', 'value': 'nurse_manager'}</t>
+          <t>Nurse Manager</t>
         </is>
       </c>
     </row>
@@ -951,12 +951,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'physician_leader',_'value':_'physician'}</t>
+          <t>physician_leader</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Physician Leader', 'value': 'physician'}</t>
+          <t>Physician Leader</t>
         </is>
       </c>
     </row>
@@ -968,12 +968,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'april_15,_2026_(virtual)',_'value':_'session_1'}</t>
+          <t>april_15,_2026_(virtual)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'April 15, 2026 (Virtual)', 'value': 'session_1'}</t>
+          <t>April 15, 2026 (Virtual)</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'april_17,_2026_(in-person)',_'value':_'session_2'}</t>
+          <t>april_17,_2026_(in-person)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'April 17, 2026 (In-Person)', 'value': 'session_2'}</t>
+          <t>April 17, 2026 (In-Person)</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'april_22,_2026_(virtual)',_'value':_'session_3'}</t>
+          <t>april_22,_2026_(virtual)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'April 22, 2026 (Virtual)', 'value': 'session_3'}</t>
+          <t>April 22, 2026 (Virtual)</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'remote_patient_monitoring_(rpm)',_'value':_'rpm'}</t>
+          <t>remote_patient_monitoring_(rpm)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Remote Patient Monitoring (RPM)', 'value': 'rpm'}</t>
+          <t>Remote Patient Monitoring (RPM)</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'electronic_health_records_(ehr)_integration',_'value':_'ehr'}</t>
+          <t>electronic_health_records_(ehr)_integration</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Electronic Health Records (EHR) Integration', 'value': 'ehr'}</t>
+          <t>Electronic Health Records (EHR) Integration</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'telehealth_platforms',_'value':_'telehealth'}</t>
+          <t>telehealth_platforms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Telehealth Platforms', 'value': 'telehealth'}</t>
+          <t>Telehealth Platforms</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'ai_and_predictive_analytics',_'value':_'ai_analytics'}</t>
+          <t>ai_and_predictive_analytics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'AI and Predictive Analytics', 'value': 'ai_analytics'}</t>
+          <t>AI and Predictive Analytics</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'mobile_patient_engagement',_'value':_'mobile_engagement'}</t>
+          <t>mobile_patient_engagement</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Mobile Patient Engagement', 'value': 'mobile_engagement'}</t>
+          <t>Mobile Patient Engagement</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'registered_and_confirmed',_'value':_'registered'}</t>
+          <t>registered_and_confirmed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Registered and Confirmed', 'value': 'registered'}</t>
+          <t>Registered and Confirmed</t>
         </is>
       </c>
     </row>
